--- a/data/performance/daily/signal_list_2026-05-11.xlsx
+++ b/data/performance/daily/signal_list_2026-05-11.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 19.0%  (23W / 98L of 121 evaluated)</t>
+          <t>Win Rate: 24.8%  (30W / 91L of 121 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
         <v>404</v>
@@ -595,10 +595,10 @@
         <v>410</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.46</v>
+        <v>-0.98</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2610</v>
+        <v>2590</v>
       </c>
       <c r="D7" t="n">
         <v>2580</v>
@@ -637,10 +637,10 @@
         <v>2640</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.15</v>
+        <v>-0.39</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4850</v>
+        <v>4700</v>
       </c>
       <c r="D9" t="n">
         <v>4390</v>
@@ -721,10 +721,10 @@
         <v>4930</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.65</v>
+        <v>4.89</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-9.48</v>
+        <v>-6.6</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="D12" t="n">
         <v>1660</v>
@@ -847,10 +847,10 @@
         <v>1675</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4560</v>
+        <v>4660</v>
       </c>
       <c r="D13" t="n">
         <v>4560</v>
@@ -889,10 +889,10 @@
         <v>4560</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D14" t="n">
         <v>350</v>
@@ -931,14 +931,14 @@
         <v>350</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16525</v>
+        <v>16575</v>
       </c>
       <c r="D21" t="n">
         <v>16625</v>
@@ -1225,10 +1225,10 @@
         <v>16850</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="D22" t="n">
         <v>1205</v>
@@ -1267,10 +1267,10 @@
         <v>1235</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.49</v>
+        <v>-0.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>-2.82</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D23" t="n">
         <v>131</v>
@@ -1309,10 +1309,10 @@
         <v>144</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-9.029999999999999</v>
+        <v>-6.43</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4540</v>
+        <v>4510</v>
       </c>
       <c r="D24" t="n">
         <v>4500</v>
@@ -1351,10 +1351,10 @@
         <v>4540</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.88</v>
+        <v>-0.22</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D25" t="n">
         <v>131</v>
@@ -1393,10 +1393,10 @@
         <v>139</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.76</v>
+        <v>-2.96</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D26" t="n">
         <v>188</v>
@@ -1435,10 +1435,10 @@
         <v>196</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.16</v>
+        <v>4.26</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D30" t="n">
         <v>630</v>
@@ -1603,10 +1603,10 @@
         <v>630</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" t="n">
         <v>111</v>
@@ -1771,10 +1771,10 @@
         <v>124</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.2</v>
+        <v>5.08</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.72</v>
+        <v>-5.93</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
         <v>97</v>
@@ -1855,10 +1855,10 @@
         <v>101</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-3.96</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1745</v>
+        <v>1740</v>
       </c>
       <c r="D39" t="n">
         <v>1730</v>
@@ -1981,10 +1981,10 @@
         <v>1750</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.86</v>
+        <v>-0.57</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3100</v>
+        <v>3060</v>
       </c>
       <c r="D40" t="n">
         <v>3070</v>
@@ -2023,14 +2023,14 @@
         <v>3110</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.33</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D41" t="n">
         <v>266</v>
@@ -2065,10 +2065,10 @@
         <v>278</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-4.32</v>
+        <v>-3.62</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D45" t="n">
         <v>334</v>
@@ -2233,10 +2233,10 @@
         <v>368</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.79</v>
+        <v>3.95</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-6.7</v>
+        <v>-5.65</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D46" t="n">
         <v>252</v>
@@ -2275,10 +2275,10 @@
         <v>260</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-3.08</v>
+        <v>-2.33</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6275</v>
+        <v>6225</v>
       </c>
       <c r="D47" t="n">
         <v>6375</v>
@@ -2317,10 +2317,10 @@
         <v>6375</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>700</v>
+        <v>760</v>
       </c>
       <c r="D49" t="n">
         <v>695</v>
@@ -2401,10 +2401,10 @@
         <v>830</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>18.57</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.71</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="D51" t="n">
         <v>1235</v>
@@ -2485,14 +2485,14 @@
         <v>1245</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4</v>
+        <v>1.22</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.41</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="D52" t="n">
         <v>1615</v>
@@ -2527,14 +2527,14 @@
         <v>1635</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.93</v>
+        <v>2.19</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D55" t="n">
         <v>76</v>
@@ -2653,10 +2653,10 @@
         <v>79</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0</v>
+        <v>-5.95</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-3.8</v>
+        <v>-9.52</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D57" t="n">
         <v>765</v>
@@ -2737,10 +2737,10 @@
         <v>785</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3.97</v>
+        <v>4.67</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2720</v>
+        <v>2600</v>
       </c>
       <c r="D58" t="n">
         <v>2570</v>
@@ -2779,10 +2779,10 @@
         <v>2720</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-5.51</v>
+        <v>-1.15</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D60" t="n">
         <v>141</v>
@@ -2863,10 +2863,10 @@
         <v>192</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>16.36</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-19.43</v>
+        <v>-14.55</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="D62" t="n">
         <v>550</v>
@@ -2947,10 +2947,10 @@
         <v>560</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.9</v>
+        <v>1.82</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="D63" t="n">
         <v>1810</v>
@@ -2989,10 +2989,10 @@
         <v>1830</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D64" t="n">
         <v>90</v>
@@ -3031,10 +3031,10 @@
         <v>104</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2.97</v>
+        <v>5.05</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-10.89</v>
+        <v>-9.09</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D67" t="n">
         <v>82</v>
@@ -3157,10 +3157,10 @@
         <v>85</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-3.53</v>
+        <v>-1.2</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D71" t="n">
         <v>212</v>
@@ -3325,10 +3325,10 @@
         <v>230</v>
       </c>
       <c r="F71" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G71" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>-7.83</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D72" t="n">
         <v>328</v>
@@ -3367,10 +3367,10 @@
         <v>442</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>14.51</v>
+        <v>15.1</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-15.03</v>
+        <v>-14.58</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D74" t="n">
         <v>139</v>
@@ -3451,10 +3451,10 @@
         <v>151</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>11.03</v>
+        <v>12.69</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>2.21</v>
+        <v>3.73</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D76" t="n">
         <v>178</v>
@@ -3535,10 +3535,10 @@
         <v>199</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-7.77</v>
+        <v>-7.29</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D77" t="n">
         <v>53</v>
@@ -3577,10 +3577,10 @@
         <v>54</v>
       </c>
       <c r="F77" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G77" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>-1.85</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D78" t="n">
         <v>214</v>
@@ -3619,10 +3619,10 @@
         <v>244</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>8.93</v>
+        <v>3.39</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-4.46</v>
+        <v>-9.32</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
         <v>48</v>
@@ -3661,14 +3661,14 @@
         <v>49</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>4.26</v>
+        <v>-2</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D80" t="n">
         <v>110</v>
@@ -3703,10 +3703,10 @@
         <v>120</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10.09</v>
+        <v>12.15</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.92</v>
+        <v>2.8</v>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D81" t="n">
         <v>232</v>
@@ -3745,10 +3745,10 @@
         <v>264</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1.54</v>
+        <v>4.76</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>-10.77</v>
+        <v>-7.94</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" t="n">
         <v>76</v>
@@ -3913,14 +3913,14 @@
         <v>76</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.33</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D88" t="n">
         <v>276</v>
@@ -4039,10 +4039,10 @@
         <v>300</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-6.76</v>
+        <v>-4.83</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D89" t="n">
         <v>280</v>
@@ -4081,10 +4081,10 @@
         <v>300</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>4.17</v>
+        <v>2.04</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>-2.78</v>
+        <v>-4.76</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="D91" t="n">
         <v>990</v>
@@ -4165,14 +4165,14 @@
         <v>995</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.02</v>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D92" t="n">
         <v>97</v>
@@ -4207,10 +4207,10 @@
         <v>99</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>5.32</v>
+        <v>4.21</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>3.19</v>
+        <v>2.11</v>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D93" t="n">
         <v>74</v>
@@ -4249,10 +4249,10 @@
         <v>78</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>-5.13</v>
+        <v>-2.63</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D94" t="n">
         <v>81</v>
@@ -4291,10 +4291,10 @@
         <v>106</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>24.71</v>
+        <v>29.27</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-4.71</v>
+        <v>-1.22</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D96" t="n">
         <v>44</v>
@@ -4375,10 +4375,10 @@
         <v>52</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-15.38</v>
+        <v>-8.33</v>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D97" t="n">
         <v>80</v>
@@ -4417,10 +4417,10 @@
         <v>92</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>16.46</v>
+        <v>17.95</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D98" t="n">
         <v>248</v>
@@ -4459,10 +4459,10 @@
         <v>256</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-3.12</v>
+        <v>-3.88</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="D99" t="n">
         <v>910</v>
@@ -4501,10 +4501,10 @@
         <v>1035</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0.49</v>
+        <v>1.97</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>-11.65</v>
+        <v>-10.34</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D100" t="n">
         <v>133</v>
@@ -4543,10 +4543,10 @@
         <v>135</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D101" t="n">
         <v>84</v>
@@ -4585,10 +4585,10 @@
         <v>101</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1</v>
+        <v>4.12</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>-16</v>
+        <v>-13.4</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D103" t="n">
         <v>191</v>
@@ -4669,10 +4669,10 @@
         <v>202</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3.59</v>
+        <v>4.12</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>-2.05</v>
+        <v>-1.55</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D104" t="n">
         <v>84</v>
@@ -4711,10 +4711,10 @@
         <v>90</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>3.45</v>
+        <v>4.65</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-3.45</v>
+        <v>-2.33</v>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D105" t="n">
         <v>118</v>
@@ -4753,10 +4753,10 @@
         <v>133</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>5.56</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>-6.35</v>
+        <v>-4.07</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D107" t="n">
         <v>83</v>
@@ -4837,10 +4837,10 @@
         <v>96</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>-13.54</v>
+        <v>-11.7</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D108" t="n">
         <v>67</v>
@@ -4879,10 +4879,10 @@
         <v>69</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1.47</v>
+        <v>2.99</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D109" t="n">
         <v>155</v>
@@ -4921,10 +4921,10 @@
         <v>161</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>-3.73</v>
+        <v>-1.9</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D110" t="n">
         <v>184</v>
@@ -4963,10 +4963,10 @@
         <v>260</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>18.18</v>
+        <v>20.37</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-16.36</v>
+        <v>-14.81</v>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D111" t="n">
         <v>500</v>
@@ -5005,10 +5005,10 @@
         <v>530</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>4.95</v>
+        <v>3.92</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>-0.99</v>
+        <v>-1.96</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D113" t="n">
         <v>134</v>
@@ -5089,10 +5089,10 @@
         <v>153</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>-11.84</v>
+        <v>-11.26</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D115" t="n">
         <v>985</v>
@@ -5173,10 +5173,10 @@
         <v>1020</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>4.62</v>
+        <v>5.15</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D116" t="n">
         <v>224</v>
@@ -5215,10 +5215,10 @@
         <v>244</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.67</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D117" t="n">
         <v>78</v>
@@ -5257,10 +5257,10 @@
         <v>93</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>2.2</v>
+        <v>4.49</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>-14.29</v>
+        <v>-12.36</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>545</v>
+        <v>498</v>
       </c>
       <c r="D118" t="n">
         <v>515</v>
@@ -5299,14 +5299,14 @@
         <v>560</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>2.75</v>
+        <v>12.45</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.41</v>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D119" t="n">
         <v>135</v>
@@ -5341,14 +5341,14 @@
         <v>146</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>6.57</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.75</v>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D120" t="n">
         <v>179</v>
@@ -5383,14 +5383,14 @@
         <v>184</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>0.55</v>
+        <v>3.95</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.13</v>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D121" t="n">
         <v>452</v>
@@ -5425,10 +5425,10 @@
         <v>525</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>-13.9</v>
+        <v>-12.23</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D123" t="n">
         <v>585</v>
@@ -5509,10 +5509,10 @@
         <v>645</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>-7.87</v>
+        <v>-7.14</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8725</v>
+        <v>8675</v>
       </c>
       <c r="D124" t="n">
         <v>8725</v>
@@ -5551,14 +5551,14 @@
         <v>9000</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.58</v>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="D125" t="n">
         <v>2600</v>
@@ -5593,10 +5593,10 @@
         <v>2600</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>5.69</v>
+        <v>6.12</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>5.69</v>
+        <v>6.12</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-11.xlsx
+++ b/data/performance/daily/signal_list_2026-05-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-11.xlsx
+++ b/data/performance/daily/signal_list_2026-05-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-11.xlsx
+++ b/data/performance/daily/signal_list_2026-05-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J259"/>
+  <dimension ref="A1:K259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-8.09</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-4.52</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -941,12 +992,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1025,12 +1086,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1062,17 +1128,22 @@
       <c r="G17" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1109,12 +1180,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>-1.78</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1193,12 +1274,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1235,12 +1321,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1272,17 +1363,22 @@
       <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1319,12 +1415,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1361,12 +1462,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,12 +1509,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1487,12 +1603,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1566,17 +1692,22 @@
       <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1613,12 +1744,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1655,12 +1791,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1692,17 +1833,22 @@
       <c r="G32" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1739,12 +1885,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1776,17 +1927,22 @@
       <c r="G34" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,17 +1974,22 @@
       <c r="G35" s="4" t="n">
         <v>-3.77</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1860,17 +2021,22 @@
       <c r="G36" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1902,17 +2068,22 @@
       <c r="G37" s="4" t="n">
         <v>-3.59</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1949,12 +2120,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1986,17 +2162,22 @@
       <c r="G39" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2028,17 +2209,22 @@
       <c r="G40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2070,17 +2256,22 @@
       <c r="G41" s="4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2117,12 +2308,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2154,17 +2350,22 @@
       <c r="G43" s="4" t="n">
         <v>-1.32</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2201,12 +2402,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2238,17 +2444,22 @@
       <c r="G45" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2285,12 +2496,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2322,17 +2538,22 @@
       <c r="G47" s="4" t="n">
         <v>-9.23</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2369,12 +2590,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2411,12 +2637,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2453,12 +2684,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2495,12 +2731,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2537,12 +2778,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2579,12 +2825,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2616,17 +2867,22 @@
       <c r="G54" s="4" t="n">
         <v>-2.67</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2663,12 +2919,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2700,17 +2961,22 @@
       <c r="G56" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2747,12 +3013,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2789,12 +3060,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2826,17 +3102,22 @@
       <c r="G59" s="4" t="n">
         <v>-14.61</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2868,17 +3149,22 @@
       <c r="G60" s="4" t="n">
         <v>-0.37</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2915,12 +3201,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2952,17 +3243,22 @@
       <c r="G62" s="4" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2994,17 +3290,22 @@
       <c r="G63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3041,12 +3342,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3083,12 +3389,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3120,17 +3431,22 @@
       <c r="G66" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3167,12 +3483,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3209,12 +3530,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3251,12 +3577,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3293,12 +3624,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3335,12 +3671,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,12 +3718,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3419,12 +3765,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3456,17 +3807,22 @@
       <c r="G74" s="4" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3503,12 +3859,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3545,12 +3906,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3587,12 +3953,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3629,12 +4000,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3671,12 +4047,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3713,12 +4094,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3755,12 +4141,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3792,17 +4183,22 @@
       <c r="G82" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3839,12 +4235,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3881,12 +4282,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3918,17 +4324,22 @@
       <c r="G85" s="4" t="n">
         <v>-5.66</v>
       </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3960,17 +4371,22 @@
       <c r="G86" s="4" t="n">
         <v>-2.73</v>
       </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4007,12 +4423,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4044,17 +4465,22 @@
       <c r="G88" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4091,12 +4517,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4133,12 +4564,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4175,12 +4611,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4212,17 +4653,22 @@
       <c r="G92" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4254,17 +4700,22 @@
       <c r="G93" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4301,12 +4752,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4338,17 +4794,22 @@
       <c r="G95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4385,12 +4846,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4427,12 +4893,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4464,17 +4935,22 @@
       <c r="G98" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4511,12 +4987,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4548,17 +5029,22 @@
       <c r="G100" s="4" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4590,17 +5076,22 @@
       <c r="G101" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4637,12 +5128,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4679,12 +5175,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4721,12 +5222,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4758,17 +5264,22 @@
       <c r="G105" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H105" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4805,12 +5316,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4842,17 +5358,22 @@
       <c r="G107" s="4" t="n">
         <v>-3.82</v>
       </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4889,12 +5410,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4926,17 +5452,22 @@
       <c r="G109" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4973,12 +5504,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5010,17 +5546,22 @@
       <c r="G111" s="4" t="n">
         <v>-1.48</v>
       </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5057,12 +5598,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5099,12 +5645,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5136,17 +5687,22 @@
       <c r="G114" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5183,12 +5739,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5225,12 +5786,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5262,17 +5828,22 @@
       <c r="G117" s="4" t="n">
         <v>-1.15</v>
       </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5309,12 +5880,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5351,12 +5927,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5388,17 +5969,22 @@
       <c r="G120" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5435,12 +6021,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5477,12 +6068,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5514,17 +6110,22 @@
       <c r="G123" s="4" t="n">
         <v>-3.33</v>
       </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5561,12 +6162,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5603,12 +6209,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5640,17 +6251,22 @@
       <c r="G126" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5682,17 +6298,22 @@
       <c r="G127" s="4" t="n">
         <v>-3.97</v>
       </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5724,17 +6345,22 @@
       <c r="G128" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5771,12 +6397,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5813,12 +6444,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5855,12 +6491,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5897,12 +6538,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5939,12 +6585,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5981,12 +6632,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6023,12 +6679,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6065,12 +6726,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6102,17 +6768,22 @@
       <c r="G137" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6144,17 +6815,22 @@
       <c r="G138" s="4" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6191,12 +6867,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6233,12 +6914,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6270,17 +6956,22 @@
       <c r="G141" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6312,17 +7003,22 @@
       <c r="G142" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6359,12 +7055,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6396,17 +7097,22 @@
       <c r="G144" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6443,12 +7149,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6480,17 +7191,22 @@
       <c r="G146" s="4" t="n">
         <v>-1.78</v>
       </c>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6527,12 +7243,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6569,12 +7290,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6611,12 +7337,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6648,17 +7379,22 @@
       <c r="G150" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6690,17 +7426,22 @@
       <c r="G151" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H151" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6732,17 +7473,22 @@
       <c r="G152" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6779,12 +7525,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6816,17 +7567,22 @@
       <c r="G154" s="4" t="n">
         <v>-1.97</v>
       </c>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6858,17 +7614,22 @@
       <c r="G155" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6905,12 +7666,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6942,17 +7708,22 @@
       <c r="G157" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6989,12 +7760,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7026,17 +7802,22 @@
       <c r="G159" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H159" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7068,17 +7849,22 @@
       <c r="G160" s="4" t="n">
         <v>-3.59</v>
       </c>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7115,12 +7901,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7152,17 +7943,22 @@
       <c r="G162" s="4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7194,17 +7990,22 @@
       <c r="G163" s="4" t="n">
         <v>-1.32</v>
       </c>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7236,17 +8037,22 @@
       <c r="G164" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7283,12 +8089,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7325,12 +8136,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7367,12 +8183,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7404,17 +8225,22 @@
       <c r="G168" s="4" t="n">
         <v>-9.23</v>
       </c>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7451,12 +8277,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7488,17 +8319,22 @@
       <c r="G170" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7535,12 +8371,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7577,12 +8418,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7614,17 +8460,22 @@
       <c r="G173" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H173" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7661,12 +8512,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7703,12 +8559,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7740,17 +8601,22 @@
       <c r="G176" s="4" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H176" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7782,17 +8648,22 @@
       <c r="G177" s="4" t="n">
         <v>-2.67</v>
       </c>
-      <c r="H177" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7829,12 +8700,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7871,12 +8747,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7908,17 +8789,22 @@
       <c r="G180" s="4" t="n">
         <v>-3.01</v>
       </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7955,12 +8841,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7997,12 +8888,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8034,17 +8930,22 @@
       <c r="G183" s="4" t="n">
         <v>-14.61</v>
       </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8076,17 +8977,22 @@
       <c r="G184" s="4" t="n">
         <v>-0.37</v>
       </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8118,17 +9024,22 @@
       <c r="G185" s="4" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8160,17 +9071,22 @@
       <c r="G186" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8207,12 +9123,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8249,12 +9170,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8291,12 +9217,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8328,17 +9259,22 @@
       <c r="G190" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H190" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8375,12 +9311,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8417,12 +9358,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8459,12 +9405,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8501,12 +9452,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8543,12 +9499,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8585,12 +9546,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8627,12 +9593,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8669,12 +9640,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8711,12 +9687,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8753,12 +9734,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8790,17 +9776,22 @@
       <c r="G201" s="4" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H201" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8832,17 +9823,22 @@
       <c r="G202" s="4" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H202" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8879,12 +9875,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8921,12 +9922,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8963,12 +9969,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9005,12 +10016,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9047,12 +10063,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9084,17 +10105,22 @@
       <c r="G208" s="4" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H208" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9126,17 +10152,22 @@
       <c r="G209" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H209" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9173,12 +10204,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9215,12 +10251,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9257,12 +10298,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9294,17 +10340,22 @@
       <c r="G213" s="4" t="n">
         <v>-5.66</v>
       </c>
-      <c r="H213" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9336,17 +10387,22 @@
       <c r="G214" s="4" t="n">
         <v>-2.73</v>
       </c>
-      <c r="H214" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9383,12 +10439,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9425,12 +10486,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9467,12 +10533,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9509,12 +10580,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9546,17 +10622,22 @@
       <c r="G219" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H219" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9588,17 +10669,22 @@
       <c r="G220" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H220" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9630,17 +10716,22 @@
       <c r="G221" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9677,12 +10768,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9719,12 +10815,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9761,12 +10862,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9798,17 +10904,22 @@
       <c r="G225" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9845,12 +10956,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9882,17 +10998,22 @@
       <c r="G227" s="4" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H227" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9929,12 +11050,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9971,12 +11097,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10013,12 +11144,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10050,17 +11186,22 @@
       <c r="G231" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H231" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10092,17 +11233,22 @@
       <c r="G232" s="4" t="n">
         <v>-13.42</v>
       </c>
-      <c r="H232" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10139,12 +11285,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10176,17 +11327,22 @@
       <c r="G234" s="4" t="n">
         <v>-1.48</v>
       </c>
-      <c r="H234" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10223,12 +11379,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10260,17 +11421,22 @@
       <c r="G236" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H236" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10307,12 +11473,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10344,17 +11515,22 @@
       <c r="G238" s="4" t="n">
         <v>-1.15</v>
       </c>
-      <c r="H238" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I238" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10386,17 +11562,22 @@
       <c r="G239" s="4" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="H239" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10433,12 +11614,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I240" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10475,12 +11661,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10517,12 +11708,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10559,12 +11755,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10601,12 +11802,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10643,12 +11849,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10680,17 +11891,22 @@
       <c r="G246" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H246" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10722,17 +11938,22 @@
       <c r="G247" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H247" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I247" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10764,17 +11985,22 @@
       <c r="G248" s="4" t="n">
         <v>-3.97</v>
       </c>
-      <c r="H248" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10811,12 +12037,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I249" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10853,12 +12084,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I250" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10895,12 +12131,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I251" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10937,12 +12178,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I252" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10979,12 +12225,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I253" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11021,12 +12272,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I254" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11063,12 +12319,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I255" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11100,17 +12361,22 @@
       <c r="G256" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H256" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H256" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I256" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11147,12 +12413,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11184,17 +12455,22 @@
       <c r="G258" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H258" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H258" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11226,17 +12502,22 @@
       <c r="G259" s="4" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H259" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I259" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -11253,7 +12534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11263,9 +12544,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11295,7 +12577,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -11320,15 +12602,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
